--- a/outputs/statistics/inferential_statistics.xlsx
+++ b/outputs/statistics/inferential_statistics.xlsx
@@ -498,29 +498,29 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>21.9072</v>
+        <v>22.939</v>
       </c>
       <c r="D2" t="n">
-        <v>30.9902</v>
+        <v>32.0973</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1558</v>
+        <v>0.1717</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2695</v>
+        <v>0.8512</v>
       </c>
       <c r="G2" t="n">
-        <v>0.387</v>
+        <v>0.4266</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6694</v>
+        <v>2.1144</v>
       </c>
       <c r="I2" t="n">
-        <v>-50.5456</v>
+        <v>-18.2683</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>&lt; 0.001</t>
+          <t>0.002</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>41.27</v>
+        <v>14.92</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -552,29 +552,29 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>109.1814</v>
+        <v>113.9049</v>
       </c>
       <c r="D3" t="n">
-        <v>146.8042</v>
+        <v>155.3709</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2561</v>
+        <v>2.121</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1914</v>
+        <v>7.0283</v>
       </c>
       <c r="G3" t="n">
-        <v>3.1203</v>
+        <v>5.2689</v>
       </c>
       <c r="H3" t="n">
-        <v>2.9597</v>
+        <v>17.4593</v>
       </c>
       <c r="I3" t="n">
-        <v>-37.6399</v>
+        <v>-9.783099999999999</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>&lt; 0.001</t>
+          <t>0.006</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>30.73</v>
+        <v>7.99</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -606,29 +606,29 @@
         <v>100</v>
       </c>
       <c r="C4" t="n">
-        <v>217.5992</v>
+        <v>231.0414</v>
       </c>
       <c r="D4" t="n">
-        <v>289.2519</v>
+        <v>306.829</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7697</v>
+        <v>8.074999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2514</v>
+        <v>14.1667</v>
       </c>
       <c r="G4" t="n">
-        <v>4.3961</v>
+        <v>20.0594</v>
       </c>
       <c r="H4" t="n">
-        <v>5.5929</v>
+        <v>35.192</v>
       </c>
       <c r="I4" t="n">
-        <v>-43.3379</v>
+        <v>-8.0501</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>&lt; 0.001</t>
+          <t>0.003</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>35.39</v>
+        <v>6.57</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -660,25 +660,25 @@
         <v>200</v>
       </c>
       <c r="C5" t="n">
-        <v>437.0723</v>
+        <v>465.434</v>
       </c>
       <c r="D5" t="n">
-        <v>571.6188</v>
+        <v>615.0842</v>
       </c>
       <c r="E5" t="n">
-        <v>1.045</v>
+        <v>18.295</v>
       </c>
       <c r="F5" t="n">
-        <v>4.4944</v>
+        <v>20.3224</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5959</v>
+        <v>45.4473</v>
       </c>
       <c r="H5" t="n">
-        <v>11.1648</v>
+        <v>50.4837</v>
       </c>
       <c r="I5" t="n">
-        <v>-50.5042</v>
+        <v>-9.479200000000001</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>41.24</v>
+        <v>7.74</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -714,25 +714,25 @@
         <v>10</v>
       </c>
       <c r="C6" t="n">
-        <v>58.16</v>
+        <v>51.0005</v>
       </c>
       <c r="D6" t="n">
-        <v>28.2364</v>
+        <v>29.6151</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1994</v>
+        <v>0.3285</v>
       </c>
       <c r="F6" t="n">
-        <v>0.302</v>
+        <v>0.4494</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4954</v>
+        <v>0.8161</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7503</v>
+        <v>1.1164</v>
       </c>
       <c r="I6" t="n">
-        <v>143.2042</v>
+        <v>66.53870000000001</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>116.93</v>
+        <v>54.33</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -768,25 +768,25 @@
         <v>50</v>
       </c>
       <c r="C7" t="n">
-        <v>287.5274</v>
+        <v>251.5815</v>
       </c>
       <c r="D7" t="n">
-        <v>140.1308</v>
+        <v>146.9127</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6692</v>
+        <v>2.3042</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5603</v>
+        <v>0.8781</v>
       </c>
       <c r="G7" t="n">
-        <v>4.1465</v>
+        <v>5.724</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3919</v>
+        <v>2.1813</v>
       </c>
       <c r="I7" t="n">
-        <v>144.9974</v>
+        <v>73.5206</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>118.39</v>
+        <v>60.03</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -822,25 +822,25 @@
         <v>100</v>
       </c>
       <c r="C8" t="n">
-        <v>576.2745</v>
+        <v>497.1928</v>
       </c>
       <c r="D8" t="n">
-        <v>284.6817</v>
+        <v>292.1759</v>
       </c>
       <c r="E8" t="n">
-        <v>3.2143</v>
+        <v>1.3951</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5165</v>
+        <v>1.1662</v>
       </c>
       <c r="G8" t="n">
-        <v>7.9849</v>
+        <v>3.4657</v>
       </c>
       <c r="H8" t="n">
-        <v>3.7671</v>
+        <v>2.897</v>
       </c>
       <c r="I8" t="n">
-        <v>142.1042</v>
+        <v>195.2874</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>116.03</v>
+        <v>159.45</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -876,25 +876,25 @@
         <v>200</v>
       </c>
       <c r="C9" t="n">
-        <v>1154.3518</v>
+        <v>997.8037</v>
       </c>
       <c r="D9" t="n">
-        <v>566.2318</v>
+        <v>608.8069</v>
       </c>
       <c r="E9" t="n">
-        <v>6.9734</v>
+        <v>4.7438</v>
       </c>
       <c r="F9" t="n">
-        <v>4.4712</v>
+        <v>17.771</v>
       </c>
       <c r="G9" t="n">
-        <v>17.3228</v>
+        <v>11.7843</v>
       </c>
       <c r="H9" t="n">
-        <v>11.1072</v>
+        <v>44.1456</v>
       </c>
       <c r="I9" t="n">
-        <v>122.971</v>
+        <v>36.6309</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>100.41</v>
+        <v>29.91</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -930,29 +930,29 @@
         <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>168.2898</v>
+        <v>167.5279</v>
       </c>
       <c r="D10" t="n">
-        <v>166.2843</v>
+        <v>172.5385</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1401</v>
+        <v>0.1051</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3454</v>
+        <v>0.3814</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3481</v>
+        <v>0.2612</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8581</v>
+        <v>0.9474</v>
       </c>
       <c r="I10" t="n">
-        <v>9.3178</v>
+        <v>-21.9365</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>0.001</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>7.61</v>
+        <v>17.91</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Microservices</t>
+          <t>Monolithic</t>
         </is>
       </c>
     </row>
@@ -984,29 +984,29 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>845.4108</v>
+        <v>841.3066</v>
       </c>
       <c r="D11" t="n">
-        <v>831.205</v>
+        <v>876.1563</v>
       </c>
       <c r="E11" t="n">
-        <v>3.6321</v>
+        <v>6.7395</v>
       </c>
       <c r="F11" t="n">
-        <v>3.5253</v>
+        <v>4.3701</v>
       </c>
       <c r="G11" t="n">
-        <v>9.0227</v>
+        <v>16.7418</v>
       </c>
       <c r="H11" t="n">
-        <v>8.757300000000001</v>
+        <v>10.856</v>
       </c>
       <c r="I11" t="n">
-        <v>4.8611</v>
+        <v>-7.5148</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.003</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.97</v>
+        <v>6.14</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Microservices</t>
+          <t>Monolithic</t>
         </is>
       </c>
     </row>
@@ -1038,47 +1038,47 @@
         <v>100</v>
       </c>
       <c r="C12" t="n">
-        <v>1687.1515</v>
+        <v>1739.7198</v>
       </c>
       <c r="D12" t="n">
-        <v>1658.5813</v>
+        <v>1737.5137</v>
       </c>
       <c r="E12" t="n">
-        <v>6.7131</v>
+        <v>27.6628</v>
       </c>
       <c r="F12" t="n">
-        <v>3.1467</v>
+        <v>18.8152</v>
       </c>
       <c r="G12" t="n">
-        <v>16.6762</v>
+        <v>68.7182</v>
       </c>
       <c r="H12" t="n">
-        <v>7.8169</v>
+        <v>46.7395</v>
       </c>
       <c r="I12" t="n">
-        <v>6.6745</v>
+        <v>0.1142</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.915</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>5.45</v>
+        <v>0.09</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>Negligible</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Microservices</t>
+          <t>No Significant Difference</t>
         </is>
       </c>
     </row>
@@ -1092,29 +1092,29 @@
         <v>200</v>
       </c>
       <c r="C13" t="n">
-        <v>3359.5275</v>
+        <v>3408.5001</v>
       </c>
       <c r="D13" t="n">
-        <v>3309.1049</v>
+        <v>3494.0021</v>
       </c>
       <c r="E13" t="n">
-        <v>3.692</v>
+        <v>1.6635</v>
       </c>
       <c r="F13" t="n">
-        <v>7.4832</v>
+        <v>4.3611</v>
       </c>
       <c r="G13" t="n">
-        <v>9.1715</v>
+        <v>4.1324</v>
       </c>
       <c r="H13" t="n">
-        <v>18.5892</v>
+        <v>10.8336</v>
       </c>
       <c r="I13" t="n">
-        <v>10.4663</v>
+        <v>-31.7279</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>&lt; 0.001</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>8.550000000000001</v>
+        <v>25.91</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Microservices</t>
+          <t>Monolithic</t>
         </is>
       </c>
     </row>
@@ -1146,29 +1146,29 @@
         <v>10</v>
       </c>
       <c r="C14" t="n">
-        <v>18.362</v>
+        <v>16.4387</v>
       </c>
       <c r="D14" t="n">
-        <v>16.1579</v>
+        <v>17.598</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1997</v>
+        <v>0.0416</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2918</v>
+        <v>0.3408</v>
       </c>
       <c r="G14" t="n">
-        <v>0.496</v>
+        <v>0.1035</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7248</v>
+        <v>0.8465</v>
       </c>
       <c r="I14" t="n">
-        <v>10.7971</v>
+        <v>-5.8489</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>&lt; 0.001</t>
+          <t>0.026</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>8.82</v>
+        <v>4.78</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Microservices</t>
+          <t>Monolithic</t>
         </is>
       </c>
     </row>
@@ -1200,29 +1200,29 @@
         <v>50</v>
       </c>
       <c r="C15" t="n">
-        <v>90.7616</v>
+        <v>80.74379999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>82.3991</v>
+        <v>85.06310000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3142</v>
+        <v>0.9185</v>
       </c>
       <c r="F15" t="n">
-        <v>0.273</v>
+        <v>1.4661</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7806</v>
+        <v>2.2817</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6782</v>
+        <v>3.6419</v>
       </c>
       <c r="I15" t="n">
-        <v>34.7965</v>
+        <v>-4.3243</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>&lt; 0.001</t>
+          <t>0.018</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>28.41</v>
+        <v>3.53</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Microservices</t>
+          <t>Monolithic</t>
         </is>
       </c>
     </row>
@@ -1254,29 +1254,29 @@
         <v>100</v>
       </c>
       <c r="C16" t="n">
-        <v>180.8162</v>
+        <v>157.1795</v>
       </c>
       <c r="D16" t="n">
-        <v>162.5197</v>
+        <v>163.9348</v>
       </c>
       <c r="E16" t="n">
-        <v>5.4407</v>
+        <v>0.6975</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5708</v>
+        <v>0.7933</v>
       </c>
       <c r="G16" t="n">
-        <v>13.5155</v>
+        <v>1.7327</v>
       </c>
       <c r="H16" t="n">
-        <v>6.3862</v>
+        <v>1.9706</v>
       </c>
       <c r="I16" t="n">
-        <v>5.2664</v>
+        <v>-11.0766</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>&lt; 0.001</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1285,7 +1285,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.3</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Microservices</t>
+          <t>Monolithic</t>
         </is>
       </c>
     </row>
@@ -1308,29 +1308,29 @@
         <v>200</v>
       </c>
       <c r="C17" t="n">
-        <v>358.6946</v>
+        <v>309.6399</v>
       </c>
       <c r="D17" t="n">
-        <v>317.3085</v>
+        <v>321.5698</v>
       </c>
       <c r="E17" t="n">
-        <v>13.3023</v>
+        <v>1.7094</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0767</v>
+        <v>4.6972</v>
       </c>
       <c r="G17" t="n">
-        <v>33.0447</v>
+        <v>4.2463</v>
       </c>
       <c r="H17" t="n">
-        <v>2.6747</v>
+        <v>11.6685</v>
       </c>
       <c r="I17" t="n">
-        <v>5.3712</v>
+        <v>-4.1338</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>0.036</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.39</v>
+        <v>3.38</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Microservices</t>
+          <t>Monolithic</t>
         </is>
       </c>
     </row>
